--- a/templates/CeaPointsDeCollectes.xlsx
+++ b/templates/CeaPointsDeCollectes.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Dans le CEA </t>
   </si>
   <si>
-    <t xml:space="preserve">Collecte du : Collecte du : {{Date_Collecte}}</t>
+    <t xml:space="preserve">Collecte du : {{Date_Collecte}}</t>
   </si>
   <si>
     <t xml:space="preserve">☐ </t>
@@ -377,10 +377,11 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="12"/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -426,6 +427,7 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="5">
@@ -538,7 +540,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -929,7 +931,7 @@
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.43"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="11.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="3" width="19.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="3" width="19.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="23.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12.17"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="1" max="6" min="6" style="4" width="30.43"/>
@@ -948,7 +950,7 @@
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
     </row>
-    <row r="2" customFormat="false" ht="50" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="49.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
